--- a/data/a_Eingangsdaten/Testdaten/Test2/test-Optimierungsgrößen-1stetig_teuer-2fluktual_billig.xlsx
+++ b/data/a_Eingangsdaten/Testdaten/Test2/test-Optimierungsgrößen-1stetig_teuer-2fluktual_billig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Testdaten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Testdaten\Test2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1259075A-83CF-4D99-85AB-BE3CBE42495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE93E6B-C9C0-4F88-A37C-816BB4896022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="405" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4395" yWindow="2400" windowWidth="28800" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Technologie</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Art</t>
   </si>
   <si>
-    <t>Effizienz</t>
-  </si>
-  <si>
     <t>Erzeuger</t>
   </si>
   <si>
@@ -89,7 +86,19 @@
     <t>billig_fluktual1</t>
   </si>
   <si>
-    <t>Kosten [€/MW]</t>
+    <t>Kosten [Mio.€/GW]</t>
+  </si>
+  <si>
+    <t>Wirkungsgrad</t>
+  </si>
+  <si>
+    <t>Selbstentladungsrate [%/Tag]</t>
+  </si>
+  <si>
+    <t>C-Rate</t>
+  </si>
+  <si>
+    <t>Lebensdauer</t>
   </si>
 </sst>
 </file>
@@ -413,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -426,50 +435,59 @@
     <col min="10" max="10" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -483,19 +501,22 @@
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -509,19 +530,22 @@
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -534,6 +558,9 @@
       </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
